--- a/TCLAutoTestTool/bin/LDM调试和自检表模板.xlsx
+++ b/TCLAutoTestTool/bin/LDM调试和自检表模板.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="132">
   <si>
     <t>序号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -185,10 +185,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>全白电流</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>逻辑分析仪读取数据</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -201,22 +197,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>L32电流</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>电流测试</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Boost电流</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>拐点电流</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>头码</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -245,23 +229,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Boost亮度</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>功率测试</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>逻辑分析仪读取头码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>头/尾码数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>头/尾码规格</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -475,6 +447,106 @@
   <si>
     <t xml:space="preserve">                                                                                                                                                                                                                                                        版本：V1.0
                                                                                                                                                                                                                                                                         修改日期：20251128</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>机型名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平分区数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>垂直分区数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动IC型号及支持最大电流</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动IC 0对应的电流值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动IC步幅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boost窗口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据格式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据传输时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拐点电流/RGB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全白电流/RGB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L32电流/RGB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boost电流/RGB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全白色点x</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全白色点y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boost亮度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L32色点x</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>L32色点y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boost色点x</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boost色点y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>背光延迟图像测试(新机芯需要)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>总数据量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对新机芯，用光感探头测试背光延迟图像时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -588,7 +660,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -855,11 +927,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -935,6 +1020,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1037,7 +1132,38 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1329,36 +1455,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
+      <c r="A3" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="41"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="40"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44"/>
     </row>
     <row r="5" spans="1:5" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
@@ -1523,7 +1649,7 @@
         <v>31</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E15" s="11"/>
     </row>
@@ -1576,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="21"/>
@@ -1587,78 +1713,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="51"/>
+      <c r="A1" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="55"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="58"/>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="37"/>
+      <c r="A3" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="37"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48" t="s">
+      <c r="C5" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="49" t="s">
+      <c r="H5" s="53" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="58"/>
-      <c r="B6" s="62"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="49"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="53"/>
     </row>
     <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
@@ -1667,12 +1793,12 @@
       <c r="B7" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
+      <c r="C7" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
       <c r="G7" s="16"/>
       <c r="H7" s="11"/>
     </row>
@@ -1683,80 +1809,76 @@
       <c r="B8" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
+      <c r="C8" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
       <c r="G8" s="16"/>
       <c r="H8" s="11"/>
     </row>
-    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <v>3</v>
       </c>
-      <c r="B9" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B9" s="31"/>
+      <c r="C9" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="75"/>
+      <c r="E9" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="75"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <v>4</v>
       </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="75"/>
+      <c r="E10" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" s="75"/>
       <c r="G10" s="16"/>
       <c r="H10" s="11"/>
     </row>
-    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <v>5</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="75"/>
+      <c r="E11" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="75"/>
       <c r="G11" s="16"/>
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <v>6</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="75"/>
+      <c r="E12" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" s="75"/>
       <c r="G12" s="16"/>
       <c r="H12" s="11"/>
     </row>
@@ -1764,51 +1886,53 @@
       <c r="A13" s="25">
         <v>7</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="11"/>
+      <c r="B13" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
         <v>8</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>97</v>
-      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="11"/>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
         <v>9</v>
       </c>
-      <c r="B15" s="59"/>
+      <c r="B15" s="63"/>
       <c r="C15" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
+        <v>117</v>
+      </c>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
       <c r="G15" s="16"/>
       <c r="H15" s="11"/>
     </row>
@@ -1816,13 +1940,13 @@
       <c r="A16" s="25">
         <v>10</v>
       </c>
-      <c r="B16" s="59"/>
+      <c r="B16" s="63"/>
       <c r="C16" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
+        <v>118</v>
+      </c>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
       <c r="G16" s="16"/>
       <c r="H16" s="11"/>
     </row>
@@ -1830,57 +1954,53 @@
       <c r="A17" s="25">
         <v>11</v>
       </c>
-      <c r="B17" s="59" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>97</v>
-      </c>
+      <c r="B17" s="63"/>
+      <c r="C17" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="25">
         <v>12</v>
       </c>
-      <c r="B18" s="59"/>
-      <c r="C18" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="11"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="25">
         <v>13</v>
       </c>
-      <c r="B19" s="59"/>
+      <c r="B19" s="63"/>
       <c r="C19" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
+        <v>129</v>
+      </c>
+      <c r="D19" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
       <c r="G19" s="16"/>
       <c r="H19" s="11"/>
     </row>
@@ -1888,13 +2008,15 @@
       <c r="A20" s="25">
         <v>14</v>
       </c>
-      <c r="B20" s="59"/>
+      <c r="B20" s="63"/>
       <c r="C20" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
+        <v>45</v>
+      </c>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="68" t="s">
+        <v>127</v>
+      </c>
       <c r="G20" s="16"/>
       <c r="H20" s="11"/>
     </row>
@@ -1902,51 +2024,57 @@
       <c r="A21" s="25">
         <v>15</v>
       </c>
-      <c r="B21" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>97</v>
-      </c>
+      <c r="B21" s="63"/>
+      <c r="C21" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="16"/>
+      <c r="H21" s="11"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="25">
         <v>16</v>
       </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="11"/>
+      <c r="B22" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="25">
         <v>17</v>
       </c>
-      <c r="B23" s="59"/>
+      <c r="B23" s="63"/>
       <c r="C23" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
       <c r="G23" s="16"/>
       <c r="H23" s="11"/>
     </row>
@@ -1954,13 +2082,17 @@
       <c r="A24" s="25">
         <v>18</v>
       </c>
-      <c r="B24" s="59"/>
+      <c r="B24" s="63"/>
       <c r="C24" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="29"/>
+      <c r="F24" s="68" t="s">
+        <v>127</v>
+      </c>
       <c r="G24" s="16"/>
       <c r="H24" s="11"/>
     </row>
@@ -1968,33 +2100,33 @@
       <c r="A25" s="25">
         <v>19</v>
       </c>
-      <c r="B25" s="59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>97</v>
-      </c>
+      <c r="B25" s="63"/>
+      <c r="C25" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="29"/>
+      <c r="F25" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="16"/>
+      <c r="H25" s="11"/>
     </row>
     <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="25">
         <v>20</v>
       </c>
-      <c r="B26" s="59"/>
+      <c r="B26" s="63"/>
       <c r="C26" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
+        <v>51</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="29"/>
+      <c r="F26" s="67"/>
       <c r="G26" s="16"/>
       <c r="H26" s="11"/>
     </row>
@@ -2002,13 +2134,17 @@
       <c r="A27" s="25">
         <v>21</v>
       </c>
-      <c r="B27" s="59"/>
+      <c r="B27" s="63"/>
       <c r="C27" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
+        <v>123</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="29"/>
+      <c r="F27" s="68" t="s">
+        <v>127</v>
+      </c>
       <c r="G27" s="16"/>
       <c r="H27" s="11"/>
     </row>
@@ -2016,37 +2152,33 @@
       <c r="A28" s="25">
         <v>22</v>
       </c>
-      <c r="B28" s="59" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="G28" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="H28" s="24" t="s">
-        <v>97</v>
-      </c>
+      <c r="B28" s="63"/>
+      <c r="C28" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="29"/>
+      <c r="F28" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" s="16"/>
+      <c r="H28" s="11"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="25">
         <v>23</v>
       </c>
-      <c r="B29" s="59"/>
+      <c r="B29" s="63"/>
       <c r="C29" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="63"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+        <v>122</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="29"/>
+      <c r="F29" s="67"/>
       <c r="G29" s="16"/>
       <c r="H29" s="11"/>
     </row>
@@ -2054,13 +2186,17 @@
       <c r="A30" s="25">
         <v>24</v>
       </c>
-      <c r="B30" s="59"/>
+      <c r="B30" s="63"/>
       <c r="C30" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" s="63"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+        <v>125</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="29"/>
+      <c r="F30" s="68" t="s">
+        <v>127</v>
+      </c>
       <c r="G30" s="16"/>
       <c r="H30" s="11"/>
     </row>
@@ -2068,13 +2204,17 @@
       <c r="A31" s="25">
         <v>25</v>
       </c>
-      <c r="B31" s="59"/>
+      <c r="B31" s="63"/>
       <c r="C31" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="63"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+        <v>126</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="29"/>
+      <c r="F31" s="68" t="s">
+        <v>127</v>
+      </c>
       <c r="G31" s="16"/>
       <c r="H31" s="11"/>
     </row>
@@ -2082,47 +2222,47 @@
       <c r="A32" s="25">
         <v>26</v>
       </c>
-      <c r="B32" s="59"/>
-      <c r="C32" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" s="63"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="11"/>
+      <c r="B32" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="25">
-        <v>28</v>
-      </c>
-      <c r="B33" s="59" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="G33" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="H33" s="24" t="s">
-        <v>97</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B33" s="63"/>
+      <c r="C33" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="11"/>
     </row>
     <row r="34" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="25">
-        <v>29</v>
-      </c>
-      <c r="B34" s="59"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="63"/>
       <c r="C34" s="17" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
@@ -2132,11 +2272,11 @@
     </row>
     <row r="35" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="25">
-        <v>30</v>
-      </c>
-      <c r="B35" s="59"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="63"/>
       <c r="C35" s="17" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
@@ -2146,220 +2286,443 @@
     </row>
     <row r="36" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="25">
-        <v>31</v>
-      </c>
-      <c r="B36" s="59" t="s">
-        <v>80</v>
+        <v>30</v>
+      </c>
+      <c r="B36" s="63" t="s">
+        <v>57</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="56"/>
-      <c r="F36" s="57"/>
+        <v>35</v>
+      </c>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
       <c r="G36" s="27" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="25">
-        <v>32</v>
-      </c>
-      <c r="B37" s="59"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="63"/>
       <c r="C37" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="E37" s="42"/>
-      <c r="F37" s="43"/>
+        <v>58</v>
+      </c>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
       <c r="G37" s="16"/>
       <c r="H37" s="11"/>
     </row>
     <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="25">
-        <v>33</v>
-      </c>
-      <c r="B38" s="59"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="63"/>
       <c r="C38" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="E38" s="42"/>
-      <c r="F38" s="43"/>
+        <v>59</v>
+      </c>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
       <c r="G38" s="16"/>
       <c r="H38" s="11"/>
     </row>
-    <row r="39" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="25">
+        <v>33</v>
+      </c>
+      <c r="B39" s="69" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G39" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H39" s="24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="25">
         <v>34</v>
       </c>
-      <c r="B39" s="59"/>
-      <c r="C39" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="42"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="11"/>
-    </row>
-    <row r="40" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A40" s="25">
-        <v>35</v>
-      </c>
-      <c r="B40" s="59"/>
+      <c r="B40" s="73"/>
       <c r="C40" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" s="42"/>
-      <c r="F40" s="43"/>
+        <v>61</v>
+      </c>
+      <c r="D40" s="29"/>
+      <c r="E40" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F40" s="17"/>
       <c r="G40" s="16"/>
       <c r="H40" s="11"/>
     </row>
-    <row r="41" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="25">
-        <v>36</v>
-      </c>
-      <c r="B41" s="59"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="73"/>
       <c r="C41" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E41" s="42"/>
-      <c r="F41" s="43"/>
+        <v>62</v>
+      </c>
+      <c r="D41" s="29"/>
+      <c r="E41" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" s="17"/>
       <c r="G41" s="16"/>
       <c r="H41" s="11"/>
     </row>
-    <row r="42" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25">
-        <v>37</v>
-      </c>
-      <c r="B42" s="59"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="73"/>
       <c r="C42" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="E42" s="42"/>
-      <c r="F42" s="43"/>
+        <v>63</v>
+      </c>
+      <c r="D42" s="29"/>
+      <c r="E42" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" s="17"/>
       <c r="G42" s="16"/>
       <c r="H42" s="11"/>
     </row>
-    <row r="43" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="25">
-        <v>38</v>
-      </c>
-      <c r="B43" s="59"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="73"/>
       <c r="C43" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="E43" s="42"/>
-      <c r="F43" s="43"/>
+        <v>64</v>
+      </c>
+      <c r="D43" s="29"/>
+      <c r="E43" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F43" s="17"/>
       <c r="G43" s="16"/>
       <c r="H43" s="11"/>
     </row>
-    <row r="44" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="25">
-        <v>39</v>
-      </c>
-      <c r="B44" s="59"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="74"/>
       <c r="C44" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="E44" s="42"/>
-      <c r="F44" s="43"/>
+        <v>115</v>
+      </c>
+      <c r="D44" s="29"/>
+      <c r="E44" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F44" s="17"/>
       <c r="G44" s="16"/>
       <c r="H44" s="11"/>
     </row>
     <row r="45" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="25">
+        <v>39</v>
+      </c>
+      <c r="B45" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="25">
         <v>40</v>
       </c>
-      <c r="B45" s="59"/>
-      <c r="C45" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" s="42"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="11"/>
-    </row>
-    <row r="46" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="26">
+      <c r="B46" s="63"/>
+      <c r="C46" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="11"/>
+    </row>
+    <row r="47" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="25">
         <v>41</v>
       </c>
-      <c r="B46" s="60"/>
-      <c r="C46" s="19" t="s">
+      <c r="B47" s="63"/>
+      <c r="C47" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="11"/>
+    </row>
+    <row r="48" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A48" s="25">
+        <v>42</v>
+      </c>
+      <c r="B48" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="E48" s="60"/>
+      <c r="F48" s="61"/>
+      <c r="G48" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="E46" s="46"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="20"/>
+      <c r="H48" s="24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="25">
+        <v>43</v>
+      </c>
+      <c r="B49" s="63"/>
+      <c r="C49" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="46"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="11"/>
+    </row>
+    <row r="50" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A50" s="25">
+        <v>44</v>
+      </c>
+      <c r="B50" s="63"/>
+      <c r="C50" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E50" s="46"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="11"/>
+    </row>
+    <row r="51" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A51" s="25">
+        <v>45</v>
+      </c>
+      <c r="B51" s="63"/>
+      <c r="C51" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="E51" s="46"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="11"/>
+    </row>
+    <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A52" s="25">
+        <v>46</v>
+      </c>
+      <c r="B52" s="63"/>
+      <c r="C52" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="E52" s="46"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="11"/>
+    </row>
+    <row r="53" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A53" s="25">
+        <v>47</v>
+      </c>
+      <c r="B53" s="63"/>
+      <c r="C53" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="E53" s="46"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="11"/>
+    </row>
+    <row r="54" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A54" s="25">
+        <v>48</v>
+      </c>
+      <c r="B54" s="63"/>
+      <c r="C54" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54" s="46"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="11"/>
+    </row>
+    <row r="55" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="25">
+        <v>49</v>
+      </c>
+      <c r="B55" s="63"/>
+      <c r="C55" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="E55" s="46"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="11"/>
+    </row>
+    <row r="56" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="25">
+        <v>50</v>
+      </c>
+      <c r="B56" s="63"/>
+      <c r="C56" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D56" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="E56" s="46"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="11"/>
+    </row>
+    <row r="57" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A57" s="25">
+        <v>51</v>
+      </c>
+      <c r="B57" s="63"/>
+      <c r="C57" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="E57" s="46"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="11"/>
+    </row>
+    <row r="58" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A58" s="25">
+        <v>52</v>
+      </c>
+      <c r="B58" s="69"/>
+      <c r="C58" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="D58" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" s="77"/>
+      <c r="F58" s="78"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="72"/>
+    </row>
+    <row r="59" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="26">
+        <v>53</v>
+      </c>
+      <c r="B59" s="64"/>
+      <c r="C59" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="E59" s="50"/>
+      <c r="F59" s="51"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="B36:B46"/>
+  <mergeCells count="29">
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B48:B59"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C5:F6"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B32"/>
-    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="B22:B31"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B45:B47"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H4"/>
-    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D48:F48"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="B39:B44"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D58:F58"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G8 G10:G13 G15:G16 G18:G20 G22:G24 G26:G27 G29:G32 G34:G35 G37:G46">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G12 G14:G17 G19:G21 G23:G31 G33:G35 G37:G38 G40:G44 G46:G47 G49:G59">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/TCLAutoTestTool/bin/LDM调试和自检表模板.xlsx
+++ b/TCLAutoTestTool/bin/LDM调试和自检表模板.xlsx
@@ -1030,6 +1030,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1075,6 +1089,60 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1085,74 +1153,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1455,36 +1455,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="38"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="47"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
     </row>
     <row r="5" spans="1:5" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
@@ -1713,78 +1713,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="55"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="65"/>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
+      <c r="A4" s="45"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="47"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52" t="s">
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="53" t="s">
+      <c r="H5" s="60" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="62"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="53"/>
+      <c r="A6" s="69"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="60"/>
     </row>
     <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
@@ -1793,12 +1793,12 @@
       <c r="B7" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
       <c r="G7" s="16"/>
       <c r="H7" s="11"/>
     </row>
@@ -1809,12 +1809,12 @@
       <c r="B8" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
       <c r="G8" s="16"/>
       <c r="H8" s="11"/>
     </row>
@@ -1826,11 +1826,11 @@
       <c r="C9" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="75"/>
+      <c r="D9" s="38"/>
       <c r="E9" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="F9" s="75"/>
+      <c r="F9" s="38"/>
       <c r="G9" s="16"/>
       <c r="H9" s="11"/>
     </row>
@@ -1842,11 +1842,11 @@
       <c r="C10" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="75"/>
+      <c r="D10" s="38"/>
       <c r="E10" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="F10" s="75"/>
+      <c r="F10" s="38"/>
       <c r="G10" s="16"/>
       <c r="H10" s="11"/>
     </row>
@@ -1858,11 +1858,11 @@
       <c r="C11" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="75"/>
+      <c r="D11" s="38"/>
       <c r="E11" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="F11" s="75"/>
+      <c r="F11" s="38"/>
       <c r="G11" s="16"/>
       <c r="H11" s="11"/>
     </row>
@@ -1874,11 +1874,11 @@
       <c r="C12" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="75"/>
+      <c r="D12" s="38"/>
       <c r="E12" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="F12" s="75"/>
+      <c r="F12" s="38"/>
       <c r="G12" s="16"/>
       <c r="H12" s="11"/>
     </row>
@@ -1886,7 +1886,7 @@
       <c r="A13" s="25">
         <v>7</v>
       </c>
-      <c r="B13" s="63" t="s">
+      <c r="B13" s="54" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="23" t="s">
@@ -1912,7 +1912,7 @@
       <c r="A14" s="25">
         <v>8</v>
       </c>
-      <c r="B14" s="63"/>
+      <c r="B14" s="54"/>
       <c r="C14" s="17" t="s">
         <v>116</v>
       </c>
@@ -1926,7 +1926,7 @@
       <c r="A15" s="25">
         <v>9</v>
       </c>
-      <c r="B15" s="63"/>
+      <c r="B15" s="54"/>
       <c r="C15" s="17" t="s">
         <v>117</v>
       </c>
@@ -1940,7 +1940,7 @@
       <c r="A16" s="25">
         <v>10</v>
       </c>
-      <c r="B16" s="63"/>
+      <c r="B16" s="54"/>
       <c r="C16" s="17" t="s">
         <v>118</v>
       </c>
@@ -1954,7 +1954,7 @@
       <c r="A17" s="25">
         <v>11</v>
       </c>
-      <c r="B17" s="63"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="17" t="s">
         <v>119</v>
       </c>
@@ -1968,7 +1968,7 @@
       <c r="A18" s="25">
         <v>12</v>
       </c>
-      <c r="B18" s="63"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="23" t="s">
         <v>36</v>
       </c>
@@ -1992,11 +1992,11 @@
       <c r="A19" s="25">
         <v>13</v>
       </c>
-      <c r="B19" s="63"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="68" t="s">
+      <c r="D19" s="34" t="s">
         <v>127</v>
       </c>
       <c r="E19" s="29"/>
@@ -2008,13 +2008,13 @@
       <c r="A20" s="25">
         <v>14</v>
       </c>
-      <c r="B20" s="63"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="17" t="s">
         <v>45</v>
       </c>
       <c r="D20" s="29"/>
       <c r="E20" s="29"/>
-      <c r="F20" s="68" t="s">
+      <c r="F20" s="34" t="s">
         <v>127</v>
       </c>
       <c r="G20" s="16"/>
@@ -2024,13 +2024,13 @@
       <c r="A21" s="25">
         <v>15</v>
       </c>
-      <c r="B21" s="63"/>
+      <c r="B21" s="54"/>
       <c r="C21" s="17" t="s">
         <v>46</v>
       </c>
       <c r="D21" s="29"/>
       <c r="E21" s="29"/>
-      <c r="F21" s="68" t="s">
+      <c r="F21" s="34" t="s">
         <v>127</v>
       </c>
       <c r="G21" s="16"/>
@@ -2040,7 +2040,7 @@
       <c r="A22" s="25">
         <v>16</v>
       </c>
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="54" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="23" t="s">
@@ -2066,7 +2066,7 @@
       <c r="A23" s="25">
         <v>17</v>
       </c>
-      <c r="B23" s="63"/>
+      <c r="B23" s="54"/>
       <c r="C23" s="17" t="s">
         <v>50</v>
       </c>
@@ -2082,7 +2082,7 @@
       <c r="A24" s="25">
         <v>18</v>
       </c>
-      <c r="B24" s="63"/>
+      <c r="B24" s="54"/>
       <c r="C24" s="17" t="s">
         <v>120</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>90</v>
       </c>
       <c r="E24" s="29"/>
-      <c r="F24" s="68" t="s">
+      <c r="F24" s="34" t="s">
         <v>127</v>
       </c>
       <c r="G24" s="16"/>
@@ -2100,7 +2100,7 @@
       <c r="A25" s="25">
         <v>19</v>
       </c>
-      <c r="B25" s="63"/>
+      <c r="B25" s="54"/>
       <c r="C25" s="17" t="s">
         <v>121</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>90</v>
       </c>
       <c r="E25" s="29"/>
-      <c r="F25" s="68" t="s">
+      <c r="F25" s="34" t="s">
         <v>127</v>
       </c>
       <c r="G25" s="16"/>
@@ -2118,7 +2118,7 @@
       <c r="A26" s="25">
         <v>20</v>
       </c>
-      <c r="B26" s="63"/>
+      <c r="B26" s="54"/>
       <c r="C26" s="17" t="s">
         <v>51</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>90</v>
       </c>
       <c r="E26" s="29"/>
-      <c r="F26" s="67"/>
+      <c r="F26" s="33"/>
       <c r="G26" s="16"/>
       <c r="H26" s="11"/>
     </row>
@@ -2134,7 +2134,7 @@
       <c r="A27" s="25">
         <v>21</v>
       </c>
-      <c r="B27" s="63"/>
+      <c r="B27" s="54"/>
       <c r="C27" s="17" t="s">
         <v>123</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>90</v>
       </c>
       <c r="E27" s="29"/>
-      <c r="F27" s="68" t="s">
+      <c r="F27" s="34" t="s">
         <v>127</v>
       </c>
       <c r="G27" s="16"/>
@@ -2152,7 +2152,7 @@
       <c r="A28" s="25">
         <v>22</v>
       </c>
-      <c r="B28" s="63"/>
+      <c r="B28" s="54"/>
       <c r="C28" s="17" t="s">
         <v>124</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>90</v>
       </c>
       <c r="E28" s="29"/>
-      <c r="F28" s="68" t="s">
+      <c r="F28" s="34" t="s">
         <v>127</v>
       </c>
       <c r="G28" s="16"/>
@@ -2170,7 +2170,7 @@
       <c r="A29" s="25">
         <v>23</v>
       </c>
-      <c r="B29" s="63"/>
+      <c r="B29" s="54"/>
       <c r="C29" s="17" t="s">
         <v>122</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>90</v>
       </c>
       <c r="E29" s="29"/>
-      <c r="F29" s="67"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="16"/>
       <c r="H29" s="11"/>
     </row>
@@ -2186,7 +2186,7 @@
       <c r="A30" s="25">
         <v>24</v>
       </c>
-      <c r="B30" s="63"/>
+      <c r="B30" s="54"/>
       <c r="C30" s="17" t="s">
         <v>125</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>90</v>
       </c>
       <c r="E30" s="29"/>
-      <c r="F30" s="68" t="s">
+      <c r="F30" s="34" t="s">
         <v>127</v>
       </c>
       <c r="G30" s="16"/>
@@ -2204,7 +2204,7 @@
       <c r="A31" s="25">
         <v>25</v>
       </c>
-      <c r="B31" s="63"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="17" t="s">
         <v>126</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>90</v>
       </c>
       <c r="E31" s="29"/>
-      <c r="F31" s="68" t="s">
+      <c r="F31" s="34" t="s">
         <v>127</v>
       </c>
       <c r="G31" s="16"/>
@@ -2222,7 +2222,7 @@
       <c r="A32" s="25">
         <v>26</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="54" t="s">
         <v>52</v>
       </c>
       <c r="C32" s="23" t="s">
@@ -2246,7 +2246,7 @@
       <c r="A33" s="25">
         <v>27</v>
       </c>
-      <c r="B33" s="63"/>
+      <c r="B33" s="54"/>
       <c r="C33" s="17" t="s">
         <v>54</v>
       </c>
@@ -2260,7 +2260,7 @@
       <c r="A34" s="25">
         <v>28</v>
       </c>
-      <c r="B34" s="63"/>
+      <c r="B34" s="54"/>
       <c r="C34" s="17" t="s">
         <v>55</v>
       </c>
@@ -2274,7 +2274,7 @@
       <c r="A35" s="25">
         <v>29</v>
       </c>
-      <c r="B35" s="63"/>
+      <c r="B35" s="54"/>
       <c r="C35" s="17" t="s">
         <v>56</v>
       </c>
@@ -2288,7 +2288,7 @@
       <c r="A36" s="25">
         <v>30</v>
       </c>
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="54" t="s">
         <v>57</v>
       </c>
       <c r="C36" s="23" t="s">
@@ -2308,7 +2308,7 @@
       <c r="A37" s="25">
         <v>31</v>
       </c>
-      <c r="B37" s="63"/>
+      <c r="B37" s="54"/>
       <c r="C37" s="17" t="s">
         <v>58</v>
       </c>
@@ -2322,7 +2322,7 @@
       <c r="A38" s="25">
         <v>32</v>
       </c>
-      <c r="B38" s="63"/>
+      <c r="B38" s="54"/>
       <c r="C38" s="17" t="s">
         <v>59</v>
       </c>
@@ -2336,7 +2336,7 @@
       <c r="A39" s="25">
         <v>33</v>
       </c>
-      <c r="B39" s="69" t="s">
+      <c r="B39" s="55" t="s">
         <v>60</v>
       </c>
       <c r="C39" s="23" t="s">
@@ -2362,7 +2362,7 @@
       <c r="A40" s="25">
         <v>34</v>
       </c>
-      <c r="B40" s="73"/>
+      <c r="B40" s="70"/>
       <c r="C40" s="17" t="s">
         <v>61</v>
       </c>
@@ -2378,7 +2378,7 @@
       <c r="A41" s="25">
         <v>35</v>
       </c>
-      <c r="B41" s="73"/>
+      <c r="B41" s="70"/>
       <c r="C41" s="17" t="s">
         <v>62</v>
       </c>
@@ -2394,7 +2394,7 @@
       <c r="A42" s="25">
         <v>36</v>
       </c>
-      <c r="B42" s="73"/>
+      <c r="B42" s="70"/>
       <c r="C42" s="17" t="s">
         <v>63</v>
       </c>
@@ -2410,7 +2410,7 @@
       <c r="A43" s="25">
         <v>37</v>
       </c>
-      <c r="B43" s="73"/>
+      <c r="B43" s="70"/>
       <c r="C43" s="17" t="s">
         <v>64</v>
       </c>
@@ -2426,7 +2426,7 @@
       <c r="A44" s="25">
         <v>38</v>
       </c>
-      <c r="B44" s="74"/>
+      <c r="B44" s="71"/>
       <c r="C44" s="17" t="s">
         <v>115</v>
       </c>
@@ -2442,7 +2442,7 @@
       <c r="A45" s="25">
         <v>39</v>
       </c>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="54" t="s">
         <v>67</v>
       </c>
       <c r="C45" s="23" t="s">
@@ -2466,7 +2466,7 @@
       <c r="A46" s="25">
         <v>40</v>
       </c>
-      <c r="B46" s="63"/>
+      <c r="B46" s="54"/>
       <c r="C46" s="17" t="s">
         <v>69</v>
       </c>
@@ -2480,7 +2480,7 @@
       <c r="A47" s="25">
         <v>41</v>
       </c>
-      <c r="B47" s="63"/>
+      <c r="B47" s="54"/>
       <c r="C47" s="17" t="s">
         <v>70</v>
       </c>
@@ -2494,17 +2494,17 @@
       <c r="A48" s="25">
         <v>42</v>
       </c>
-      <c r="B48" s="63" t="s">
+      <c r="B48" s="54" t="s">
         <v>73</v>
       </c>
       <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="D48" s="59" t="s">
+      <c r="D48" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="E48" s="60"/>
-      <c r="F48" s="61"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="68"/>
       <c r="G48" s="27" t="s">
         <v>90</v>
       </c>
@@ -2516,15 +2516,15 @@
       <c r="A49" s="25">
         <v>43</v>
       </c>
-      <c r="B49" s="63"/>
+      <c r="B49" s="54"/>
       <c r="C49" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="D49" s="45" t="s">
+      <c r="D49" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="E49" s="46"/>
-      <c r="F49" s="47"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="53"/>
       <c r="G49" s="16"/>
       <c r="H49" s="11"/>
     </row>
@@ -2532,15 +2532,15 @@
       <c r="A50" s="25">
         <v>44</v>
       </c>
-      <c r="B50" s="63"/>
+      <c r="B50" s="54"/>
       <c r="C50" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="D50" s="45" t="s">
+      <c r="D50" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="E50" s="46"/>
-      <c r="F50" s="47"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="53"/>
       <c r="G50" s="16"/>
       <c r="H50" s="11"/>
     </row>
@@ -2548,15 +2548,15 @@
       <c r="A51" s="25">
         <v>45</v>
       </c>
-      <c r="B51" s="63"/>
+      <c r="B51" s="54"/>
       <c r="C51" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D51" s="45" t="s">
+      <c r="D51" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="E51" s="46"/>
-      <c r="F51" s="47"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="53"/>
       <c r="G51" s="16"/>
       <c r="H51" s="11"/>
     </row>
@@ -2564,15 +2564,15 @@
       <c r="A52" s="25">
         <v>46</v>
       </c>
-      <c r="B52" s="63"/>
+      <c r="B52" s="54"/>
       <c r="C52" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="45" t="s">
+      <c r="D52" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="46"/>
-      <c r="F52" s="47"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="53"/>
       <c r="G52" s="16"/>
       <c r="H52" s="11"/>
     </row>
@@ -2580,15 +2580,15 @@
       <c r="A53" s="25">
         <v>47</v>
       </c>
-      <c r="B53" s="63"/>
+      <c r="B53" s="54"/>
       <c r="C53" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D53" s="45" t="s">
+      <c r="D53" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="E53" s="46"/>
-      <c r="F53" s="47"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="53"/>
       <c r="G53" s="16"/>
       <c r="H53" s="11"/>
     </row>
@@ -2596,15 +2596,15 @@
       <c r="A54" s="25">
         <v>48</v>
       </c>
-      <c r="B54" s="63"/>
+      <c r="B54" s="54"/>
       <c r="C54" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D54" s="45" t="s">
+      <c r="D54" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="E54" s="46"/>
-      <c r="F54" s="47"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="53"/>
       <c r="G54" s="16"/>
       <c r="H54" s="11"/>
     </row>
@@ -2612,15 +2612,15 @@
       <c r="A55" s="25">
         <v>49</v>
       </c>
-      <c r="B55" s="63"/>
+      <c r="B55" s="54"/>
       <c r="C55" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D55" s="48" t="s">
+      <c r="D55" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="E55" s="46"/>
-      <c r="F55" s="47"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="53"/>
       <c r="G55" s="16"/>
       <c r="H55" s="11"/>
     </row>
@@ -2628,15 +2628,15 @@
       <c r="A56" s="25">
         <v>50</v>
       </c>
-      <c r="B56" s="63"/>
+      <c r="B56" s="54"/>
       <c r="C56" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D56" s="48" t="s">
+      <c r="D56" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="E56" s="46"/>
-      <c r="F56" s="47"/>
+      <c r="E56" s="52"/>
+      <c r="F56" s="53"/>
       <c r="G56" s="16"/>
       <c r="H56" s="11"/>
     </row>
@@ -2644,15 +2644,15 @@
       <c r="A57" s="25">
         <v>51</v>
       </c>
-      <c r="B57" s="63"/>
+      <c r="B57" s="54"/>
       <c r="C57" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="45" t="s">
+      <c r="D57" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="E57" s="46"/>
-      <c r="F57" s="47"/>
+      <c r="E57" s="52"/>
+      <c r="F57" s="53"/>
       <c r="G57" s="16"/>
       <c r="H57" s="11"/>
     </row>
@@ -2660,8 +2660,8 @@
       <c r="A58" s="25">
         <v>52</v>
       </c>
-      <c r="B58" s="69"/>
-      <c r="C58" s="70" t="s">
+      <c r="B58" s="55"/>
+      <c r="C58" s="35" t="s">
         <v>128</v>
       </c>
       <c r="D58" s="76" t="s">
@@ -2669,27 +2669,40 @@
       </c>
       <c r="E58" s="77"/>
       <c r="F58" s="78"/>
-      <c r="G58" s="71"/>
-      <c r="H58" s="72"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="37"/>
     </row>
     <row r="59" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="26">
         <v>53</v>
       </c>
-      <c r="B59" s="64"/>
+      <c r="B59" s="56"/>
       <c r="C59" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="D59" s="49" t="s">
+      <c r="D59" s="73" t="s">
         <v>103</v>
       </c>
-      <c r="E59" s="50"/>
-      <c r="F59" s="51"/>
+      <c r="E59" s="74"/>
+      <c r="F59" s="75"/>
       <c r="G59" s="28"/>
       <c r="H59" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="B39:B44"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="B48:B59"/>
     <mergeCell ref="C7:F7"/>
@@ -2705,20 +2718,7 @@
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="B39:B44"/>
     <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D58:F58"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
